--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536321_LIGAREGULARB_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536321_LIGAREGULARB_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,67 +973,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.2959</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.0588</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.2371</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8836000000000001</v>
+        <v>-0.0532</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2918</v>
+        <v>1.4783</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5918</v>
+        <v>-1.5315</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2918</v>
+        <v>1.1688</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5918</v>
+        <v>-0.4729</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.7492</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.3095</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1.0587</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-2.6713</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-4.1096</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.4384</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.2533</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.8766</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.3767</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.7671</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.5959</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.8288</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,58 +1056,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8836000000000001</v>
+        <v>-0.3047</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8836000000000001</v>
+        <v>-0.1907</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0.114</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8836000000000001</v>
+        <v>-0.3523</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2918</v>
+        <v>-0.6362</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5918</v>
+        <v>0.2838</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8836000000000001</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2918</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5918</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.3523</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.6362</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.2838</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.2055</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.2055</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.1907</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.0329</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2959</v>
+        <v>-0.9032</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0588</v>
+        <v>-0.2994</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2371</v>
+        <v>-0.6038</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0532</v>
+        <v>-0.657</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4783</v>
+        <v>-0.034</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5315</v>
+        <v>-0.623</v>
       </c>
       <c r="J9" t="n">
-        <v>0.696</v>
+        <v>-0.5923</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1688</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4729</v>
+        <v>-0.0383</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7492</v>
+        <v>-0.0648</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3095</v>
+        <v>0.5199</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0587</v>
+        <v>-0.5847</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.6713</v>
+        <v>1.0274</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.1096</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4384</v>
+        <v>1.0274</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2533</v>
+        <v>-0.3352</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8766</v>
+        <v>0.0532</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3767</v>
+        <v>-0.3884</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7671</v>
+        <v>-0.9384</v>
       </c>
       <c r="W9" t="n">
-        <v>2.5959</v>
+        <v>0.2397</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8288</v>
+        <v>-1.1781</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,67 +1222,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3047</v>
+        <v>-1.1826</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1907</v>
+        <v>-1.404</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.114</v>
+        <v>0.2214</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3523</v>
+        <v>-0.0455</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6362</v>
+        <v>-0.4713</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2838</v>
+        <v>0.4257</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.2021</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.2816</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.0795</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3523</v>
+        <v>0.1566</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6362</v>
+        <v>-0.1896</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2838</v>
+        <v>0.3463</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2055</v>
+        <v>-0.411</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2055</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1578</v>
+        <v>-0.1371</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1907</v>
+        <v>-0.1745</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0329</v>
+        <v>0.0374</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.589</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.589</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>P. CARRENO VIDAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9032</v>
+        <v>-1.7853</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2994</v>
+        <v>-2.1054</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6038</v>
+        <v>0.3201</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.657</v>
+        <v>-0.6619</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.034</v>
+        <v>-0.7255</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.623</v>
+        <v>0.0636</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5923</v>
+        <v>0.2916</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.1835</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0383</v>
+        <v>0.4751</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0648</v>
+        <v>-0.9535</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5199</v>
+        <v>-0.542</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5847</v>
+        <v>-0.4116</v>
       </c>
       <c r="P11" t="n">
-        <v>1.0274</v>
+        <v>-1.2329</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.0548</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0274</v>
+        <v>0.8219</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3352</v>
+        <v>0.5684</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0532</v>
+        <v>0.1167</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3884</v>
+        <v>0.4517</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9384</v>
+        <v>-0.4589</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2397</v>
+        <v>-0.4589</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1781</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. CARRENO VIDAL</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,67 +1388,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7853</v>
+        <v>-3.929</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1054</v>
+        <v>-4.3727</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3201</v>
+        <v>0.4437</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6619</v>
+        <v>0.0334</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7255</v>
+        <v>-1.5836</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0636</v>
+        <v>1.617</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2916</v>
+        <v>0.1141</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1835</v>
+        <v>-1.6618</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4751</v>
+        <v>1.7759</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9535</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.542</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4116</v>
+        <v>-0.1589</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.2329</v>
+        <v>-3.9041</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0548</v>
+        <v>-5.137</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8219</v>
+        <v>1.2329</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5684</v>
+        <v>-0.4076</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1167</v>
+        <v>-0.5278</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4517</v>
+        <v>0.1202</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.4589</v>
+        <v>0.3493</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.4589</v>
+        <v>1.1781</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.8288</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. GARCIA RIERA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1471,150 +1471,146 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0662</v>
+        <v>8.449199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2876</v>
+        <v>6.219700000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2214</v>
+        <v>2.2296</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.9291</v>
+        <v>11.4078</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.763</v>
+        <v>3.914599999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.166</v>
+        <v>7.493000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.0857</v>
+        <v>15.08</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5734</v>
+        <v>4.025</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5123</v>
+        <v>11.055</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1566</v>
+        <v>-3.6724</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1896</v>
+        <v>-0.1103</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3463</v>
+        <v>-3.562</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.411</v>
+        <v>-10.2741</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0274</v>
+        <v>-19.5206</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6163999999999999</v>
+        <v>9.246600000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1371</v>
+        <v>2.713</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1745</v>
+        <v>1.9139</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0374</v>
+        <v>0.7989999999999998</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.589</v>
+        <v>4.6027</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>8.746600000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.589</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>play_by_play_2536321_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-4.1438</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. COSTA I VAZQUEZ</t>
+          <t>A. ARAGONES NAVAIS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TQ-CB PRAT</t>
+          <t>PROINBENI UPB GANDIA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.8126</v>
+        <v>5.0154</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.2563</v>
+        <v>2.9592</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4437</v>
+        <v>2.0563</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8502</v>
+        <v>4.9372</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.8753</v>
+        <v>4.3767</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0252</v>
+        <v>0.5606</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7695</v>
+        <v>4.8234</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.9536</v>
+        <v>4.3877</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1841</v>
+        <v>0.4357</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.08069999999999999</v>
+        <v>0.1139</v>
       </c>
       <c r="N14" t="n">
-        <v>0.07829999999999999</v>
+        <v>-0.011</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1589</v>
+        <v>0.1249</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.9041</v>
+        <v>1.8493</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.137</v>
+        <v>-1.2329</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2329</v>
+        <v>3.0822</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4076</v>
+        <v>-0.3533</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5278</v>
+        <v>-0.6313</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1202</v>
+        <v>0.278</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3493</v>
+        <v>-1.4178</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1781</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8288</v>
+        <v>-1.4178</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1625,86 +1621,90 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. LOPEZ-SANVICENTE RETA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TQ-CB PRAT</t>
+          <t>PROINBENI UPB GANDIA</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.449200000000003</v>
+        <v>1.6338</v>
       </c>
       <c r="E15" t="n">
-        <v>6.219700000000002</v>
+        <v>1.7635</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2296</v>
+        <v>-0.1297</v>
       </c>
       <c r="G15" t="n">
-        <v>11.4078</v>
+        <v>-0.6496</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9148</v>
+        <v>0.2825</v>
       </c>
       <c r="I15" t="n">
-        <v>7.493100000000001</v>
+        <v>-0.9321</v>
       </c>
       <c r="J15" t="n">
-        <v>15.08</v>
+        <v>0.9664</v>
       </c>
       <c r="K15" t="n">
-        <v>4.024999999999999</v>
+        <v>0.8085</v>
       </c>
       <c r="L15" t="n">
-        <v>11.055</v>
+        <v>0.1578</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.6724</v>
+        <v>-1.616</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1103</v>
+        <v>-0.5261</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.562000000000001</v>
+        <v>-1.0899</v>
       </c>
       <c r="P15" t="n">
-        <v>-10.2741</v>
+        <v>2.0548</v>
       </c>
       <c r="Q15" t="n">
-        <v>-19.5206</v>
+        <v>-0.2055</v>
       </c>
       <c r="R15" t="n">
-        <v>9.246600000000001</v>
+        <v>2.2603</v>
       </c>
       <c r="S15" t="n">
-        <v>2.713000000000001</v>
+        <v>0.9272</v>
       </c>
       <c r="T15" t="n">
-        <v>1.913899999999999</v>
+        <v>0.5232</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7989999999999999</v>
+        <v>0.404</v>
       </c>
       <c r="V15" t="n">
-        <v>4.602700000000001</v>
+        <v>-0.6986</v>
       </c>
       <c r="W15" t="n">
-        <v>8.746600000000001</v>
+        <v>0.4794</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.1438</v>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+        <v>-1.1781</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2536321_LIGAREGULARB_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ARAGONES NAVAIS</t>
+          <t>J. WELLS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.0154</v>
+        <v>1.1716</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9592</v>
+        <v>1.2805</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0563</v>
+        <v>-0.1089</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9372</v>
+        <v>-2.2243</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3767</v>
+        <v>-1.2074</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5606</v>
+        <v>-1.0169</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8234</v>
+        <v>0.3018</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3877</v>
+        <v>-0.1344</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4357</v>
+        <v>0.4363</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1139</v>
+        <v>-2.5261</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.011</v>
+        <v>-1.0729</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1249</v>
+        <v>-1.4532</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8493</v>
+        <v>3.4932</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.2329</v>
+        <v>-0.2055</v>
       </c>
       <c r="R16" t="n">
-        <v>3.0822</v>
+        <v>3.6987</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3533</v>
+        <v>-0.5562</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6313</v>
+        <v>-0.2337</v>
       </c>
       <c r="U16" t="n">
-        <v>0.278</v>
+        <v>-0.3226</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4178</v>
+        <v>0.4589</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4178</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4178</v>
+        <v>-0.9589</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. LOPEZ-SANVICENTE RETA</t>
+          <t>L. FERRANDO ORTELLS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6338</v>
+        <v>-0.9515</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7635</v>
+        <v>-1.7743</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1297</v>
+        <v>0.8228</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6496</v>
+        <v>0.5187</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2825</v>
+        <v>-1.3997</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9321</v>
+        <v>1.9184</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9664</v>
+        <v>0.4728</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8085</v>
+        <v>-1.0681</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1578</v>
+        <v>1.5409</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.616</v>
+        <v>0.0459</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5261</v>
+        <v>-0.3315</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0899</v>
+        <v>0.3775</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0548</v>
+        <v>1.2329</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2055</v>
+        <v>-2.2603</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2603</v>
+        <v>3.4932</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9272</v>
+        <v>-0.1072</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5232</v>
+        <v>0.0132</v>
       </c>
       <c r="U17" t="n">
-        <v>0.404</v>
+        <v>-0.1204</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6986</v>
+        <v>-2.5959</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4794</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1781</v>
+        <v>-2.5959</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. WELLS</t>
+          <t>S. MENDIOLA DIEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1716</v>
+        <v>-1.0204</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2805</v>
+        <v>-3.4216</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1089</v>
+        <v>2.4012</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2243</v>
+        <v>-2.1838</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2074</v>
+        <v>-2.3086</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0169</v>
+        <v>0.1249</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3018</v>
+        <v>-1.3667</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1344</v>
+        <v>-2.1557</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4363</v>
+        <v>0.789</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5261</v>
+        <v>-0.8171</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0729</v>
+        <v>-0.1529</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4532</v>
+        <v>-0.6642</v>
       </c>
       <c r="P18" t="n">
-        <v>3.4932</v>
+        <v>0.8219</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2055</v>
+        <v>-2.2603</v>
       </c>
       <c r="R18" t="n">
-        <v>3.6987</v>
+        <v>3.0822</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5562</v>
+        <v>0.3415</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2337</v>
+        <v>0.2054</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3226</v>
+        <v>0.1361</v>
       </c>
       <c r="V18" t="n">
-        <v>0.4589</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4178</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9589</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. FERRANDO ORTELLS</t>
+          <t>J. SANTANA LUCHORO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9515</v>
+        <v>-1.5924</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7743</v>
+        <v>-0.9469</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8228</v>
+        <v>-0.6454</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5187</v>
+        <v>-1.6759</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3997</v>
+        <v>-0.8709</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9184</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4728</v>
+        <v>0.5078</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0681</v>
+        <v>-0.203</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5409</v>
+        <v>0.7107</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0459</v>
+        <v>-2.1836</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3315</v>
+        <v>-0.668</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3775</v>
+        <v>-1.5156</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2329</v>
+        <v>0.8219</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2603</v>
+        <v>-1.0274</v>
       </c>
       <c r="R19" t="n">
-        <v>3.4932</v>
+        <v>1.8493</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1072</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0132</v>
+        <v>-0.4273</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1204</v>
+        <v>-0.3111</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.5959</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.5959</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. MENDIOLA DIEZ</t>
+          <t>F. SANTANA ROSALES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,58 +2048,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0204</v>
+        <v>-2.1618</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4216</v>
+        <v>0.6277</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4012</v>
+        <v>-2.7896</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1838</v>
+        <v>-2.1548</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.3086</v>
+        <v>-0.065</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1249</v>
+        <v>-2.0898</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3667</v>
+        <v>0.7653</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.1557</v>
+        <v>0.4085</v>
       </c>
       <c r="L20" t="n">
-        <v>0.789</v>
+        <v>0.3568</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8171</v>
+        <v>-2.92</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1529</v>
+        <v>-0.4735</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6642</v>
+        <v>-2.4466</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8219</v>
+        <v>0.411</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2603</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.0822</v>
+        <v>0.411</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3415</v>
+        <v>-0.418</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2054</v>
+        <v>-0.1375</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1361</v>
+        <v>-0.2805</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SANTANA LUCHORO</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,58 +2131,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5924</v>
+        <v>-2.1726</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9469</v>
+        <v>-1.3896</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6454</v>
+        <v>-0.783</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6759</v>
+        <v>-2.4553</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8709</v>
+        <v>-1.6662</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.789</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5078</v>
+        <v>-1.4191</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.203</v>
+        <v>-1.4191</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7107</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1836</v>
+        <v>-1.0362</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.668</v>
+        <v>-0.2471</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5156</v>
+        <v>-0.789</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8219</v>
+        <v>0.2055</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0274</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8493</v>
+        <v>0.2055</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7383999999999999</v>
+        <v>0.0772</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4273</v>
+        <v>0.0295</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3111</v>
+        <v>0.0477</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. SANTANA ROSALES</t>
+          <t>M. AMADASUN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1618</v>
+        <v>-2.8446</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6277</v>
+        <v>0.0757</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7896</v>
+        <v>-2.9202</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1548</v>
+        <v>-0.7795</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.065</v>
+        <v>1.2874</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0898</v>
+        <v>-2.0668</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7653</v>
+        <v>0.8671</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4085</v>
+        <v>1.4978</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3568</v>
+        <v>-0.6307</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.92</v>
+        <v>-1.6466</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4735</v>
+        <v>-0.2104</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.4466</v>
+        <v>-1.4362</v>
       </c>
       <c r="P22" t="n">
-        <v>0.411</v>
+        <v>-1.8493</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.0548</v>
       </c>
       <c r="R22" t="n">
-        <v>0.411</v>
+        <v>0.2055</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.418</v>
+        <v>0.3732</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1375</v>
+        <v>0.4346</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2805</v>
+        <v>-0.0613</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.589</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.8288</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.4178</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>M. BILALOVIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1726</v>
+        <v>-3.79</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3896</v>
+        <v>-1.4037</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.783</v>
+        <v>-2.3862</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4553</v>
+        <v>-4.7407</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6662</v>
+        <v>-2.3435</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.789</v>
+        <v>-2.3972</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4191</v>
+        <v>-2.2464</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.4191</v>
+        <v>-2.012</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.2344</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0362</v>
+        <v>-2.4943</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2471</v>
+        <v>-0.3315</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.789</v>
+        <v>-2.1628</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2055</v>
+        <v>1.2329</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2055</v>
+        <v>1.2329</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0772</v>
+        <v>-0.5219</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0295</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0477</v>
+        <v>0.0533</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.2397</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.4178</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.1781</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. AMADASUN</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,235 +2380,69 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8446</v>
+        <v>-6.712500000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0757</v>
+        <v>-2.2295</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9202</v>
+        <v>-4.4827</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7795</v>
+        <v>-11.408</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2874</v>
+        <v>-3.914700000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.0668</v>
+        <v>-7.492799999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8671</v>
+        <v>3.6724</v>
       </c>
       <c r="K24" t="n">
-        <v>1.4978</v>
+        <v>0.1101999999999994</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6307</v>
+        <v>3.562099999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.6466</v>
+        <v>-15.0801</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2104</v>
+        <v>-4.0249</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4362</v>
+        <v>-11.0551</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8493</v>
+        <v>10.2741</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0548</v>
+        <v>-9.246700000000001</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2055</v>
+        <v>19.5208</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3732</v>
+        <v>-0.9758999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4346</v>
+        <v>-0.799</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0613</v>
+        <v>-0.1768</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.589</v>
+        <v>-4.6027</v>
       </c>
       <c r="W24" t="n">
-        <v>0.8288</v>
+        <v>4.1438</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4178</v>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>play_by_play_2536321_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>M. BILALOVIC</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>PROINBENI UPB GANDIA</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-3.79</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-1.4037</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-2.3862</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-4.7407</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-2.3435</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-2.3972</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-2.2464</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-2.012</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-0.2344</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-2.4943</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-0.3315</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-2.1628</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.2329</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.2329</v>
-      </c>
-      <c r="S25" t="n">
-        <v>-0.5219</v>
-      </c>
-      <c r="T25" t="n">
-        <v>-0.5750999999999999</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.0533</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0.2397</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.4178</v>
-      </c>
-      <c r="X25" t="n">
-        <v>-1.1781</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536321_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>PROINBENI UPB GANDIA</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-6.712500000000001</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-2.2295</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-4.4827</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-11.408</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-3.914700000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-7.492799999999999</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.6724</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.1101999999999994</v>
-      </c>
-      <c r="L26" t="n">
-        <v>3.562099999999999</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-15.0801</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-4.0249</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-11.0551</v>
-      </c>
-      <c r="P26" t="n">
-        <v>10.2741</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-9.246700000000001</v>
-      </c>
-      <c r="R26" t="n">
-        <v>19.5208</v>
-      </c>
-      <c r="S26" t="n">
-        <v>-0.9758999999999999</v>
-      </c>
-      <c r="T26" t="n">
-        <v>-0.799</v>
-      </c>
-      <c r="U26" t="n">
-        <v>-0.1768</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-4.6027</v>
-      </c>
-      <c r="W26" t="n">
-        <v>4.1438</v>
-      </c>
-      <c r="X26" t="n">
         <v>-8.746599999999999</v>
       </c>
-      <c r="Y26" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
